--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-abandono-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-abandono-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8629" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8629" uniqueCount="512">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-put-condicional:Todas las entradas deben usar PUT condicional por identificador: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-maestros:Patient, Organization y Practitioner se envían solo con creación condicional: request.method = POST, request.url = [Tipo] y request.ifNoneExist = identifier=[system]|[value]. Nunca se actualizan. {entry.where(resource is Patient or resource is Organization or resource is Practitioner).all(request.method = 'POST' and request.ifNoneExist.startsWith('identifier=') and request.ifNoneExist.contains('|'))}urg-tx-put-condicional:Los recursos del episodio (Encounter, Condition, MedicationRequest, DocumentReference) se envían con PUT condicional: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.where((resource is Patient or resource is Organization or resource is Practitioner).not()).all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}urg-tx-sin-id:Los recursos enviados con PUT condicional no llevan Resource.id: el id lo determina el servidor al encontrar (o crear) el recurso por su identificador. {entry.where(request.method = 'PUT').all(resource.id.empty())}urg-tx-identificador:El identificador de la operación condicional (request.url o request.ifNoneExist) debe ser el mismo que trae el recurso (identifier o masterIdentifier). {entry.where(request.method = 'PUT').select(request.url.substring(request.url.indexOf('|') + 1) in (resource.identifier.value | resource.masterIdentifier.value)).allTrue() and entry.where(request.method = 'POST').select(request.ifNoneExist.substring(request.ifNoneExist.indexOf('|') + 1) in resource.identifier.value).allTrue()}urg-tx-mismo-paciente:Todos los recursos del Bundle se refieren al mismo paciente: su subject apunta a la entrada del paciente. {(entry.resource.ofType(Encounter) | entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(subject.reference = %resource.entry.where(resource is Patient).fullUrl.first())}urg-tx-restringido:Si el episodio está marcado como restringido (meta.security = R), también deben estarlo sus diagnósticos, indicaciones y documento. {entry.resource.ofType(Encounter).meta.security.where(code = 'R').exists() implies (entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(meta.security.where(system = 'http://terminology.hl7.org/CodeSystem/v3-Confidentiality' and code = 'R').exists())}urg-abandono-documento:En el abandono no hay alta: el documento es una nota de urgencia (LOINC 34111-5). {entry.resource.ofType(DocumentReference).all(type.coding.where(system = 'http://loinc.org' and code = '34111-5').exists())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -573,7 +573,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Entrada: recurso más su PUT condicional</t>
+    <t>Entrada: recurso más su operación condicional</t>
   </si>
   <si>
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
@@ -696,7 +696,7 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Operación: PUT condicional por identificador</t>
+    <t>POST con ifNoneExist (maestros) o PUT condicional (episodio)</t>
   </si>
   <si>
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
@@ -718,7 +718,7 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>PUT</t>
+    <t>POST (maestros) | PUT (episodio)</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
@@ -733,7 +733,7 @@
     <t>Bundle.entry.request.url</t>
   </si>
   <si>
-    <t>[Tipo]?identifier=[system]|[value]</t>
+    <t>[Tipo] (maestros) o [Tipo]?identifier=[sistema]|[valor] (episodio)</t>
   </si>
   <si>
     <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
@@ -769,7 +769,7 @@
     <t>Bundle.entry.request.ifNoneExist</t>
   </si>
   <si>
-    <t>For conditional creates</t>
+    <t>identifier=[sistema]|[valor] (solo maestros)</t>
   </si>
   <si>
     <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
@@ -920,7 +920,7 @@
     <t>Bundle.entry:paciente.request</t>
   </si>
   <si>
-    <t>PUT Patient?identifier=[sistema]|[valor]</t>
+    <t>POST Patient, ifNoneExist identifier=[sistema]|[valor]</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.id</t>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>Bundle.entry:paciente.request.method</t>
+  </si>
+  <si>
+    <t>POST</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.url</t>
@@ -1041,7 +1044,7 @@
     <t>Bundle.entry:establecimiento.request</t>
   </si>
   <si>
-    <t>PUT Organization?identifier=[sistema DEIS]|[código]</t>
+    <t>POST Organization, ifNoneExist identifier=[sistema DEIS]|[código]</t>
   </si>
   <si>
     <t>Bundle.entry:establecimiento.request.id</t>
@@ -1162,7 +1165,7 @@
     <t>Bundle.entry:profesional.request</t>
   </si>
   <si>
-    <t>PUT Practitioner?identifier=[sistema]|[RUN]</t>
+    <t>POST Practitioner, ifNoneExist identifier=[sistema]|[RUN]</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.request.id</t>
@@ -1254,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
+    <t>Episodio de atención en una unidad de urgencia. Se envía SIEMPRE COMPLETO en cada evento: el PUT condicional reemplaza el recurso entero, por lo que el alta y el abandono deben repetir todos los datos informados en la admisión (previsión, procedencia, medio de llegada, motivo de consulta, etc.). Un dato omitido en el alta se borra del repositorio.</t>
   </si>
   <si>
     <t>Encounter[@moodCode='EVN']</t>
@@ -1294,6 +1297,9 @@
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.method</t>
+  </si>
+  <si>
+    <t>PUT</t>
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.url</t>
@@ -5750,7 +5756,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -9374,7 +9380,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9442,7 +9448,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -9556,7 +9562,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9668,7 +9674,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9780,7 +9786,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -9892,7 +9898,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -9903,7 +9909,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -10004,7 +10010,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -10116,7 +10122,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -10228,7 +10234,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -10342,7 +10348,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -10458,7 +10464,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -10570,7 +10576,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10682,7 +10688,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10796,7 +10802,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -10910,7 +10916,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -11024,13 +11030,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -11055,7 +11061,7 @@
         <v>144</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>177</v>
@@ -11138,7 +11144,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>181</v>
@@ -11250,7 +11256,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>182</v>
@@ -11364,7 +11370,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>183</v>
@@ -11480,7 +11486,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>184</v>
@@ -11592,7 +11598,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>187</v>
@@ -11706,7 +11712,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>191</v>
@@ -11732,13 +11738,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11804,10 +11810,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11818,7 +11824,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -11930,7 +11936,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -12042,7 +12048,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -12156,7 +12162,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -12272,7 +12278,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -12386,7 +12392,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -12500,7 +12506,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12529,7 +12535,7 @@
         <v>144</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>215</v>
@@ -12612,7 +12618,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12724,7 +12730,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12838,7 +12844,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -12954,7 +12960,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -12998,7 +13004,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13066,7 +13072,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -13180,7 +13186,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -13292,7 +13298,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -13404,7 +13410,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13516,7 +13522,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13527,7 +13533,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>87</v>
@@ -13628,7 +13634,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13740,7 +13746,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13852,7 +13858,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -13966,7 +13972,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -14082,7 +14088,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -14194,7 +14200,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -14306,7 +14312,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -14420,7 +14426,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14534,7 +14540,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14648,13 +14654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -14679,7 +14685,7 @@
         <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>177</v>
@@ -14762,7 +14768,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>181</v>
@@ -14874,7 +14880,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>182</v>
@@ -14988,7 +14994,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>183</v>
@@ -15104,7 +15110,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>184</v>
@@ -15216,7 +15222,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>187</v>
@@ -15330,7 +15336,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>191</v>
@@ -15356,13 +15362,13 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15428,10 +15434,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15442,7 +15448,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>195</v>
@@ -15554,7 +15560,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>199</v>
@@ -15666,7 +15672,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>200</v>
@@ -15780,7 +15786,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>201</v>
@@ -15896,7 +15902,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>202</v>
@@ -16010,7 +16016,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>208</v>
@@ -16124,7 +16130,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>213</v>
@@ -16153,7 +16159,7 @@
         <v>144</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>215</v>
@@ -16236,7 +16242,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>217</v>
@@ -16348,7 +16354,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>218</v>
@@ -16462,7 +16468,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>219</v>
@@ -16578,7 +16584,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>220</v>
@@ -16622,7 +16628,7 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>77</v>
@@ -16690,7 +16696,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>225</v>
@@ -16804,7 +16810,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>229</v>
@@ -16916,7 +16922,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>232</v>
@@ -17028,7 +17034,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>234</v>
@@ -17140,7 +17146,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>237</v>
@@ -17151,7 +17157,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>87</v>
@@ -17252,7 +17258,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>240</v>
@@ -17364,7 +17370,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>244</v>
@@ -17476,7 +17482,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>245</v>
@@ -17590,7 +17596,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>246</v>
@@ -17706,7 +17712,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>247</v>
@@ -17818,7 +17824,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>250</v>
@@ -17930,7 +17936,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>253</v>
@@ -18044,7 +18050,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>257</v>
@@ -18158,7 +18164,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>261</v>
@@ -18272,13 +18278,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
@@ -18303,7 +18309,7 @@
         <v>144</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>177</v>
@@ -18386,7 +18392,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>181</v>
@@ -18498,7 +18504,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>182</v>
@@ -18612,7 +18618,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>183</v>
@@ -18728,7 +18734,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>184</v>
@@ -18840,7 +18846,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>187</v>
@@ -18954,14 +18960,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18980,13 +18986,13 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19055,7 +19061,7 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -19066,7 +19072,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>195</v>
@@ -19178,7 +19184,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>199</v>
@@ -19290,7 +19296,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>200</v>
@@ -19404,7 +19410,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>201</v>
@@ -19520,7 +19526,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>202</v>
@@ -19634,7 +19640,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>208</v>
@@ -19748,7 +19754,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>213</v>
@@ -19777,7 +19783,7 @@
         <v>144</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M158" t="s" s="2">
         <v>215</v>
@@ -19860,7 +19866,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>217</v>
@@ -19972,7 +19978,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>218</v>
@@ -20086,7 +20092,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>219</v>
@@ -20202,7 +20208,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>220</v>
@@ -20246,7 +20252,7 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>77</v>
@@ -20314,7 +20320,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>225</v>
@@ -20428,7 +20434,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>229</v>
@@ -20540,7 +20546,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>232</v>
@@ -20652,7 +20658,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>234</v>
@@ -20764,7 +20770,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>237</v>
@@ -20876,7 +20882,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>240</v>
@@ -20988,7 +20994,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>244</v>
@@ -21100,7 +21106,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>245</v>
@@ -21214,7 +21220,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>246</v>
@@ -21330,7 +21336,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>247</v>
@@ -21442,7 +21448,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>250</v>
@@ -21554,7 +21560,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>253</v>
@@ -21668,7 +21674,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>257</v>
@@ -21782,7 +21788,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>261</v>
@@ -21896,13 +21902,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>77</v>
@@ -21927,7 +21933,7 @@
         <v>144</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>177</v>
@@ -22010,7 +22016,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>181</v>
@@ -22122,7 +22128,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>182</v>
@@ -22236,7 +22242,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>183</v>
@@ -22352,7 +22358,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>184</v>
@@ -22464,7 +22470,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>187</v>
@@ -22578,7 +22584,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>191</v>
@@ -22604,13 +22610,13 @@
         <v>77</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22676,10 +22682,10 @@
         <v>77</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>77</v>
@@ -22690,7 +22696,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>195</v>
@@ -22802,7 +22808,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>199</v>
@@ -22914,7 +22920,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>200</v>
@@ -23028,7 +23034,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>201</v>
@@ -23144,7 +23150,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>202</v>
@@ -23258,7 +23264,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>208</v>
@@ -23372,7 +23378,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>213</v>
@@ -23401,7 +23407,7 @@
         <v>144</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M190" t="s" s="2">
         <v>215</v>
@@ -23484,7 +23490,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>217</v>
@@ -23596,7 +23602,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>218</v>
@@ -23710,7 +23716,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>219</v>
@@ -23826,7 +23832,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>220</v>
@@ -23870,7 +23876,7 @@
         <v>77</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>77</v>
@@ -23938,7 +23944,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>225</v>
@@ -24052,7 +24058,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>229</v>
@@ -24164,7 +24170,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>232</v>
@@ -24276,7 +24282,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>234</v>
@@ -24388,7 +24394,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>237</v>
@@ -24500,7 +24506,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>240</v>
@@ -24612,7 +24618,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>244</v>
@@ -24724,7 +24730,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>245</v>
@@ -24838,7 +24844,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>246</v>
@@ -24954,7 +24960,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>247</v>
@@ -25066,7 +25072,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>250</v>
@@ -25178,7 +25184,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>253</v>
@@ -25292,7 +25298,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>257</v>
@@ -25406,7 +25412,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>261</v>
@@ -25520,13 +25526,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>77</v>
@@ -25551,7 +25557,7 @@
         <v>144</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>177</v>
@@ -25634,7 +25640,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>181</v>
@@ -25746,7 +25752,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>182</v>
@@ -25860,7 +25866,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>183</v>
@@ -25976,7 +25982,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>184</v>
@@ -26088,7 +26094,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>187</v>
@@ -26202,7 +26208,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>191</v>
@@ -26228,16 +26234,16 @@
         <v>77</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -26305,10 +26311,10 @@
         <v>77</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN215" t="s" s="2">
         <v>77</v>
@@ -26316,7 +26322,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>195</v>
@@ -26428,7 +26434,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>199</v>
@@ -26540,7 +26546,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>200</v>
@@ -26654,7 +26660,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>201</v>
@@ -26770,7 +26776,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>202</v>
@@ -26884,7 +26890,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>208</v>
@@ -26998,7 +27004,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>213</v>
@@ -27027,7 +27033,7 @@
         <v>144</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M222" t="s" s="2">
         <v>215</v>
@@ -27110,7 +27116,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>217</v>
@@ -27222,7 +27228,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>218</v>
@@ -27336,7 +27342,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>219</v>
@@ -27452,7 +27458,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>220</v>
@@ -27496,7 +27502,7 @@
         <v>77</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>77</v>
@@ -27564,7 +27570,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>225</v>
@@ -27678,7 +27684,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>229</v>
@@ -27790,7 +27796,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>232</v>
@@ -27902,7 +27908,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>234</v>
@@ -28014,7 +28020,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>237</v>
@@ -28126,7 +28132,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>240</v>
@@ -28238,7 +28244,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>244</v>
@@ -28350,7 +28356,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>245</v>
@@ -28464,7 +28470,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>246</v>
@@ -28580,7 +28586,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>247</v>
@@ -28692,7 +28698,7 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>250</v>
@@ -28804,7 +28810,7 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>253</v>
@@ -28918,7 +28924,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>257</v>
@@ -29032,7 +29038,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>261</v>
@@ -29146,10 +29152,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -29172,19 +29178,19 @@
         <v>88</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O241" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>77</v>
@@ -29233,7 +29239,7 @@
         <v>77</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>78</v>
